--- a/public/uploads/project-docs/emotion-music-planning.xlsx
+++ b/public/uploads/project-docs/emotion-music-planning.xlsx
@@ -9126,7 +9126,7 @@
       </c>
       <c r="L5" s="771" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9174,7 @@
       </c>
       <c r="L6" s="771" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="L7" s="791" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9552,7 @@
       <c r="K4" s="684" t="n"/>
       <c r="L4" s="771" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>점검</t>
         </is>
       </c>
       <c r="M4" s="820" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="N4" s="771" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
       <c r="K5" s="684" t="n"/>
       <c r="L5" s="771" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>점검</t>
         </is>
       </c>
       <c r="M5" s="823" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="N5" s="771" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9652,7 +9652,7 @@
       <c r="K6" s="684" t="n"/>
       <c r="L6" s="771" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>점검</t>
         </is>
       </c>
       <c r="M6" s="825" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="N6" s="771" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9702,7 +9702,7 @@
       <c r="K7" s="684" t="n"/>
       <c r="L7" s="771" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>점검</t>
         </is>
       </c>
       <c r="M7" s="823" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="N7" s="771" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="N8" s="791" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="N9" s="791" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
